--- a/jira_export_2026-07-21.xlsx
+++ b/jira_export_2026-07-21.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>34,056 €</t>
+          <t>34,758 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -769,14 +769,14 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>8,527 €</t>
+          <t>8,677 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>25,529 €</t>
+          <t>26,081 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -2253,11 +2253,11 @@
       <c r="N21" s="13" t="n">
         <v>848.7</v>
       </c>
-      <c r="O21" s="17" t="n">
-        <v>721.395</v>
+      <c r="O21" s="13" t="n">
+        <v>1273.05</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>103.06</v>
+        <v>181.86</v>
       </c>
     </row>
     <row r="22">
@@ -8922,10 +8922,10 @@
         <v>2812.32</v>
       </c>
       <c r="O114" s="17" t="n">
-        <v>300.28</v>
+        <v>450.42</v>
       </c>
       <c r="P114" s="16" t="n">
-        <v>100.09</v>
+        <v>150.14</v>
       </c>
     </row>
     <row r="115">
@@ -13124,10 +13124,10 @@
         <v>69305.66</v>
       </c>
       <c r="O178" s="19" t="n">
-        <v>34056.275</v>
+        <v>34758.07</v>
       </c>
       <c r="P178" s="19" t="n">
-        <v>134.47</v>
+        <v>137.24</v>
       </c>
     </row>
   </sheetData>
@@ -14263,10 +14263,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>389777</v>
+        <v>389075</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>202570</v>
+        <v>201868</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>187207</v>
@@ -14288,10 +14288,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>183883</v>
+        <v>183733</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>77174</v>
+        <v>77024</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>106709</v>
@@ -14313,10 +14313,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>205893</v>
+        <v>205342</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>125395</v>
+        <v>124844</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>80498</v>

--- a/jira_export_2026-07-21.xlsx
+++ b/jira_export_2026-07-21.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>417 h</t>
+          <t>428 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>76.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1958,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>9.25</v>
+        <v>11</v>
       </c>
       <c r="L17" s="12" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>2016</v>
       </c>
       <c r="P17" s="13" t="n">
-        <v>217.95</v>
+        <v>183.27</v>
       </c>
     </row>
     <row r="18">
@@ -2382,7 +2382,7 @@
         <v>1</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L23" s="12" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         <v>3</v>
       </c>
       <c r="K60" s="15" t="n">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="L60" s="15" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>4224.5</v>
       </c>
       <c r="P60" s="16" t="n">
-        <v>563.27</v>
+        <v>497</v>
       </c>
     </row>
     <row r="61">
@@ -6758,7 +6758,7 @@
         <v>4</v>
       </c>
       <c r="K84" s="15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="L84" s="15" t="inlineStr">
         <is>
@@ -8334,7 +8334,7 @@
         <v>6</v>
       </c>
       <c r="K106" s="15" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
@@ -11410,7 +11410,7 @@
         <v>16</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="L150" s="15" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>19</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>2.88</v>
+        <v>3.62</v>
       </c>
       <c r="L156" s="15" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>19</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>2.88</v>
+        <v>3.62</v>
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
@@ -13199,7 +13199,7 @@
         <v>34758.07</v>
       </c>
       <c r="P179" s="19" t="n">
-        <v>133.55</v>
+        <v>130.06</v>
       </c>
     </row>
   </sheetData>
@@ -14190,7 +14190,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>139.25</v>
+        <v>144.75</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>32.25</v>
@@ -14199,7 +14199,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>174.5</v>
+        <v>180</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>47.75</v>
@@ -14209,7 +14209,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.0%</t>
         </is>
       </c>
     </row>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>77.25</v>
+        <v>78.75</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>6.25</v>
@@ -14229,17 +14229,17 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>84</v>
+        <v>85.5</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>15.75</v>
+        <v>17.75</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>263.34</v>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.5%</t>
         </is>
       </c>
     </row>
@@ -14251,7 +14251,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>89.58</v>
+        <v>91.33</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-07-21.xlsx
+++ b/jira_export_2026-07-21.xlsx
@@ -824,7 +824,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>428 h</t>
+          <t>431 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -838,7 +838,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -909,7 +909,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>256</t>
+          <t>257</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -2030,7 +2030,7 @@
         <v>1</v>
       </c>
       <c r="K18" s="15" t="n">
-        <v>0.25</v>
+        <v>1.25</v>
       </c>
       <c r="L18" s="15" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>29</v>
       </c>
       <c r="K163" s="12" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="L163" s="12" t="inlineStr"/>
       <c r="M163" s="12" t="inlineStr"/>
@@ -13199,7 +13199,7 @@
         <v>34758.07</v>
       </c>
       <c r="P179" s="19" t="n">
-        <v>130.06</v>
+        <v>129.45</v>
       </c>
     </row>
   </sheetData>
@@ -14193,23 +14193,23 @@
         <v>144.75</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>32.25</v>
+        <v>32.5</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>3</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>180</v>
+        <v>180.25</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>47.75</v>
+        <v>49.75</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>486.15</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>37.1%</t>
         </is>
       </c>
     </row>
@@ -14220,7 +14220,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>78.75</v>
+        <v>79.75</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>6.25</v>
@@ -14229,17 +14229,17 @@
         <v>0.5</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>85.5</v>
+        <v>86.5</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>17.75</v>
+        <v>16.75</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>263.34</v>
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.8%</t>
         </is>
       </c>
     </row>
@@ -14251,7 +14251,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>91.33</v>
+        <v>92.33</v>
       </c>
     </row>
   </sheetData>
@@ -14415,7 +14415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I18"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -14439,7 +14439,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 11 commande(s)</t>
+          <t>Épics créées ce mois — 12 commande(s)</t>
         </is>
       </c>
     </row>
@@ -14944,73 +14944,97 @@
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
+          <t>PDMDEP-34654</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34650</t>
+        </is>
+      </c>
+      <c r="C15" s="15" t="inlineStr">
+        <is>
+          <t>21/07/2026</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="inlineStr">
+        <is>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
+        </is>
+      </c>
+      <c r="E15" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="F15" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
+      <c r="G15" s="15" t="inlineStr">
+        <is>
+          <t>Services</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="inlineStr">
+        <is>
+          <t>00176582</t>
+        </is>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
           <t>PDMDEP-34499</t>
         </is>
       </c>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-34495</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>07/07/2026</t>
         </is>
       </c>
-      <c r="D15" s="15" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
-      <c r="E15" s="15" t="inlineStr">
+      <c r="E16" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="F15" s="15" t="inlineStr">
+      <c r="F16" s="12" t="inlineStr">
         <is>
           <t>Vente additionnelle</t>
         </is>
       </c>
-      <c r="G15" s="15" t="inlineStr">
+      <c r="G16" s="12" t="inlineStr">
         <is>
           <t>Services</t>
         </is>
       </c>
-      <c r="H15" s="15" t="inlineStr">
+      <c r="H16" s="12" t="inlineStr">
         <is>
           <t>00172678</t>
         </is>
       </c>
-      <c r="I15" s="26" t="n">
+      <c r="I16" s="27" t="n">
         <v>4300</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="B16" s="18" t="n"/>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>11 commande(s)</t>
-        </is>
-      </c>
-      <c r="I16" s="25" t="n">
-        <v>14910</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>TOTAL</t>
         </is>
       </c>
       <c r="B17" s="18" t="n"/>
@@ -15021,17 +15045,17 @@
       <c r="G17" s="18" t="n"/>
       <c r="H17" s="18" t="inlineStr">
         <is>
-          <t>1 commande(s)</t>
+          <t>12 commande(s)</t>
         </is>
       </c>
       <c r="I17" s="25" t="n">
-        <v>4300</v>
+        <v>14910</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="18" t="inlineStr">
         <is>
-          <t>dont GEODP</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B18" s="18" t="n"/>
@@ -15042,10 +15066,31 @@
       <c r="G18" s="18" t="n"/>
       <c r="H18" s="18" t="inlineStr">
         <is>
+          <t>2 commande(s)</t>
+        </is>
+      </c>
+      <c r="I18" s="25" t="n">
+        <v>4300</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>dont GEODP</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
           <t>10 commande(s)</t>
         </is>
       </c>
-      <c r="I18" s="25" t="n">
+      <c r="I19" s="25" t="n">
         <v>10610</v>
       </c>
     </row>

--- a/jira_export_2026-07-21.xlsx
+++ b/jira_export_2026-07-21.xlsx
@@ -729,7 +729,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>34,758 €</t>
+          <t>34,933 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -743,7 +743,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -776,7 +776,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>26,081 €</t>
+          <t>26,256 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -2046,10 +2046,10 @@
         <v>350</v>
       </c>
       <c r="O18" s="17" t="n">
-        <v>0</v>
+        <v>175</v>
       </c>
       <c r="P18" s="16" t="n">
-        <v>0</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19">
@@ -13196,10 +13196,10 @@
         <v>69305.66</v>
       </c>
       <c r="O179" s="19" t="n">
-        <v>34758.07</v>
+        <v>34933.07</v>
       </c>
       <c r="P179" s="19" t="n">
-        <v>129.45</v>
+        <v>130.1</v>
       </c>
     </row>
   </sheetData>
@@ -14336,10 +14336,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>390375</v>
+        <v>390200</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>203168</v>
+        <v>202993</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>187207</v>
@@ -14386,10 +14386,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>206642</v>
+        <v>206467</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>126144</v>
+        <v>125969</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>80498</v>
